--- a/F_Knapsack/mochila.xlsx
+++ b/F_Knapsack/mochila.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\mochila\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\F_Knapsack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA7039C-A863-4623-AF47-E93B8E5188F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A615CAA5-BDFC-4A03-8D44-3C254FC1E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -146,6 +146,33 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -153,141 +180,8 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>recursivo</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="9525" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Hoja1!$B$4:$B$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>50</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Hoja1!$E$4:$E$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.2999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.161</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.028</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.601</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>198.25399999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>307.58100000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C93A-4B84-B51C-402E3ED9E3EE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>F bruta</c:v>
           </c:tx>
@@ -764,6 +658,516 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10071536149444049"/>
+          <c:y val="0.12089997838885584"/>
+          <c:w val="0.85348743168209829"/>
+          <c:h val="0.73664137847196864"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>F. Bruta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$16:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$D$16:$D$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11265</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>524289</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22020097</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>872415233</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7B25-46E4-AF66-4924A135D45F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="536566608"/>
+        <c:axId val="536567920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="536566608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Numero de objetos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.15172304366905665"/>
+              <c:y val="0.87814746116049835"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="536567920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="536567920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Pasos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="536566608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.4274152894285414"/>
+          <c:y val="0.89542144230578924"/>
+          <c:w val="0.1843194322043426"/>
+          <c:h val="8.2068470250497086E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Pasos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
@@ -933,171 +1337,13 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7B25-46E4-AF66-4924A135D45F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>F. Bruta</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Hoja1!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Hoja1!$D$16:$D$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>11265</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>524289</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>22020097</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>872415233</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7B25-46E4-AF66-4924A135D45F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>RECURSIVO</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Hoja1!$B$4:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Hoja1!$D$4:$D$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2042</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>56353</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>803096</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16674060</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7B25-46E4-AF66-4924A135D45F}"/>
+              <c16:uniqueId val="{00000000-4557-4957-B156-AD1B3CC7ABDC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>Iterativo Memo</c:v>
           </c:tx>
@@ -1260,7 +1506,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7B25-46E4-AF66-4924A135D45F}"/>
+              <c16:uniqueId val="{00000003-4557-4957-B156-AD1B3CC7ABDC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1592,6 +1838,1025 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Pasos</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10071536149444049"/>
+          <c:y val="0.12089997838885584"/>
+          <c:w val="0.85348743168209829"/>
+          <c:h val="0.73664137847196864"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RECURSIVO</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$D$4:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56353</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>803096</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16674060</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48984833</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>308865613</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1072382146</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>62748414417</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1CA2-4606-86F4-45DE4486D2A2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="536566608"/>
+        <c:axId val="536567920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="536566608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Numero de objetos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.14690310266829756"/>
+              <c:y val="0.88377611432018222"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="536567920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="536567920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Pasos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="536566608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.41123234049261526"/>
+          <c:y val="0.88428634580415022"/>
+          <c:w val="0.19764572744432074"/>
+          <c:h val="9.3226876244224113E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>recursivo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$4:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$E$4:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.161</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.028</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.601</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>198.25399999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>307.58100000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9789-46AF-A83B-28B1EF2641EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="551179544"/>
+        <c:axId val="551184464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="551179544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>N objetos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="551184464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="551184464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="551179544"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1672,6 +2937,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
@@ -2663,6 +4048,1517 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2708,15 +5604,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>16565</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>66262</xdr:rowOff>
+      <xdr:colOff>7600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>182804</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>612425</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>133981</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>502024</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>143435</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2736,6 +5632,120 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>424543</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>399918</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>100378</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6E98EC3-331E-4679-A4B6-ED012E93BEFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600634</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>188260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>8964</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4419BE1B-7C52-4C6B-9FD0-D8B12335B5E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>564777</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161365</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>403145</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>150806</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5513DDF9-90F1-4FC2-8BA0-6F8E5FDCBCA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3008,18 +6018,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:R221"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -3033,7 +6043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>10</v>
       </c>
@@ -3047,7 +6057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>15</v>
       </c>
@@ -3061,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>20</v>
       </c>
@@ -3075,7 +6085,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>25</v>
       </c>
@@ -3089,7 +6099,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>30</v>
       </c>
@@ -3103,7 +6113,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>35</v>
       </c>
@@ -3118,7 +6128,7 @@
       </c>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>40</v>
       </c>
@@ -3132,7 +6142,7 @@
         <v>3.601</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>45</v>
       </c>
@@ -3146,7 +6156,7 @@
         <v>198.25399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>50</v>
       </c>
@@ -3160,12 +6170,12 @@
         <v>307.58100000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>10</v>
       </c>
@@ -3179,7 +6189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -3193,7 +6203,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>20</v>
       </c>
@@ -3207,7 +6217,7 @@
         <v>0.34399999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>25</v>
       </c>
@@ -3221,12 +6231,12 @@
         <v>15.922000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10</v>
       </c>
@@ -3240,7 +6250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>15</v>
       </c>
@@ -3254,7 +6264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>20</v>
       </c>
@@ -3268,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>25</v>
       </c>
@@ -3282,7 +6292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>30</v>
       </c>
@@ -3296,7 +6306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>35</v>
       </c>
@@ -3310,7 +6320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>40</v>
       </c>
@@ -3324,7 +6334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>45</v>
       </c>
@@ -3339,7 +6349,7 @@
       </c>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>50</v>
       </c>
@@ -3353,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>55</v>
       </c>
@@ -3367,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>60</v>
       </c>
@@ -3381,7 +6391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>65</v>
       </c>
@@ -3395,7 +6405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>70</v>
       </c>
@@ -3409,7 +6419,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>75</v>
       </c>
@@ -3423,7 +6433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>80</v>
       </c>
@@ -3437,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>85</v>
       </c>
@@ -3451,7 +6461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>90</v>
       </c>
@@ -3465,7 +6475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>95</v>
       </c>
@@ -3479,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>100</v>
       </c>
@@ -3493,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>105</v>
       </c>
@@ -3507,7 +6517,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>110</v>
       </c>
@@ -3521,7 +6531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>115</v>
       </c>
@@ -3535,7 +6545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>120</v>
       </c>
@@ -3549,7 +6559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>125</v>
       </c>
@@ -3563,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>130</v>
       </c>
@@ -3582,7 +6592,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>135</v>
       </c>
@@ -3608,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>140</v>
       </c>
@@ -3634,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>145</v>
       </c>
@@ -3660,7 +6670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>150</v>
       </c>
@@ -3686,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>155</v>
       </c>
@@ -3712,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>160</v>
       </c>
@@ -3738,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>165</v>
       </c>
@@ -3764,7 +6774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>170</v>
       </c>
@@ -3790,7 +6800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>175</v>
       </c>
@@ -3816,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>180</v>
       </c>
@@ -3842,7 +6852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>185</v>
       </c>
@@ -3868,7 +6878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>190</v>
       </c>
@@ -3894,7 +6904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>195</v>
       </c>
@@ -3920,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>200</v>
       </c>
@@ -3946,7 +6956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>205</v>
       </c>
@@ -3972,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>210</v>
       </c>
@@ -3998,7 +7008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>215</v>
       </c>
@@ -4024,7 +7034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>220</v>
       </c>
@@ -4050,7 +7060,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>225</v>
       </c>
@@ -4076,7 +7086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>230</v>
       </c>
@@ -4090,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>235</v>
       </c>
@@ -4104,7 +7114,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>240</v>
       </c>
@@ -4118,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>245</v>
       </c>
@@ -4132,7 +7142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>250</v>
       </c>
@@ -4146,7 +7156,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>255</v>
       </c>
@@ -4160,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>260</v>
       </c>
@@ -4174,7 +7184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>265</v>
       </c>
@@ -4188,7 +7198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>270</v>
       </c>
@@ -4202,7 +7212,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>275</v>
       </c>
@@ -4216,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>280</v>
       </c>
@@ -4230,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>285</v>
       </c>
@@ -4244,7 +7254,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>290</v>
       </c>
@@ -4258,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>295</v>
       </c>
@@ -4272,7 +7282,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>300</v>
       </c>
@@ -4286,7 +7296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>305</v>
       </c>
@@ -4300,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>310</v>
       </c>
@@ -4314,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>315</v>
       </c>
@@ -4328,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>320</v>
       </c>
@@ -4342,7 +7352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>325</v>
       </c>
@@ -4356,7 +7366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>330</v>
       </c>
@@ -4370,7 +7380,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>335</v>
       </c>
@@ -4384,7 +7394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>340</v>
       </c>
@@ -4398,7 +7408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>345</v>
       </c>
@@ -4412,7 +7422,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>350</v>
       </c>
@@ -4426,7 +7436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>355</v>
       </c>
@@ -4440,7 +7450,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>360</v>
       </c>
@@ -4454,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>365</v>
       </c>
@@ -4468,7 +7478,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>370</v>
       </c>
@@ -4482,7 +7492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>375</v>
       </c>
@@ -4496,7 +7506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>380</v>
       </c>
@@ -4510,7 +7520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>385</v>
       </c>
@@ -4524,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>390</v>
       </c>
@@ -4538,7 +7548,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>395</v>
       </c>
@@ -4552,7 +7562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>400</v>
       </c>
@@ -4566,7 +7576,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>405</v>
       </c>
@@ -4580,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>410</v>
       </c>
@@ -4594,7 +7604,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>415</v>
       </c>
@@ -4608,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>420</v>
       </c>
@@ -4622,7 +7632,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>425</v>
       </c>
@@ -4636,7 +7646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>430</v>
       </c>
@@ -4650,7 +7660,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>435</v>
       </c>
@@ -4664,7 +7674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>440</v>
       </c>
@@ -4678,7 +7688,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>445</v>
       </c>
@@ -4692,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>450</v>
       </c>
@@ -4706,7 +7716,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>455</v>
       </c>
@@ -4720,7 +7730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>460</v>
       </c>
@@ -4734,7 +7744,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>465</v>
       </c>
@@ -4748,7 +7758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>470</v>
       </c>
@@ -4762,7 +7772,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>475</v>
       </c>
@@ -4776,7 +7786,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>480</v>
       </c>
@@ -4790,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>485</v>
       </c>
@@ -4804,7 +7814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>490</v>
       </c>
@@ -4818,7 +7828,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>495</v>
       </c>
@@ -4832,7 +7842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>500</v>
       </c>
@@ -4846,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>505</v>
       </c>
@@ -4860,7 +7870,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>510</v>
       </c>
@@ -4874,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>515</v>
       </c>
@@ -4888,7 +7898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>520</v>
       </c>
@@ -4902,7 +7912,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>525</v>
       </c>
@@ -4916,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>530</v>
       </c>
@@ -4930,7 +7940,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>535</v>
       </c>
@@ -4944,7 +7954,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>540</v>
       </c>
@@ -4958,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>545</v>
       </c>
@@ -4972,7 +7982,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>550</v>
       </c>
@@ -4986,7 +7996,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>555</v>
       </c>
@@ -5000,7 +8010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>560</v>
       </c>
@@ -5014,7 +8024,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>565</v>
       </c>
@@ -5028,7 +8038,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>570</v>
       </c>
@@ -5042,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>575</v>
       </c>
@@ -5056,7 +8066,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>580</v>
       </c>
@@ -5070,7 +8080,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>585</v>
       </c>
@@ -5084,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>590</v>
       </c>
@@ -5098,7 +8108,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>595</v>
       </c>
@@ -5112,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>600</v>
       </c>
@@ -5126,7 +8136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>605</v>
       </c>
@@ -5140,7 +8150,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>610</v>
       </c>
@@ -5154,7 +8164,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>615</v>
       </c>
@@ -5168,7 +8178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>620</v>
       </c>
@@ -5182,7 +8192,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>625</v>
       </c>
@@ -5196,7 +8206,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>630</v>
       </c>
@@ -5210,7 +8220,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>635</v>
       </c>
@@ -5224,7 +8234,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>640</v>
       </c>
@@ -5238,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>645</v>
       </c>
@@ -5252,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>650</v>
       </c>
@@ -5266,7 +8276,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>655</v>
       </c>
@@ -5280,7 +8290,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>660</v>
       </c>
@@ -5294,7 +8304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>665</v>
       </c>
@@ -5308,7 +8318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>670</v>
       </c>
@@ -5322,7 +8332,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>675</v>
       </c>
@@ -5336,7 +8346,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>680</v>
       </c>
@@ -5350,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>685</v>
       </c>
@@ -5364,7 +8374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>690</v>
       </c>
@@ -5378,7 +8388,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>695</v>
       </c>
@@ -5392,7 +8402,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>700</v>
       </c>
@@ -5406,7 +8416,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>705</v>
       </c>
@@ -5420,7 +8430,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>710</v>
       </c>
@@ -5434,7 +8444,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>715</v>
       </c>
@@ -5448,7 +8458,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>720</v>
       </c>
@@ -5462,7 +8472,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>725</v>
       </c>
@@ -5476,7 +8486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>730</v>
       </c>
@@ -5490,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>735</v>
       </c>
@@ -5504,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>740</v>
       </c>
@@ -5518,7 +8528,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>745</v>
       </c>
@@ -5532,7 +8542,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>750</v>
       </c>
@@ -5546,7 +8556,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>755</v>
       </c>
@@ -5560,7 +8570,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>760</v>
       </c>
@@ -5574,7 +8584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>765</v>
       </c>
@@ -5588,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>770</v>
       </c>
@@ -5602,7 +8612,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>775</v>
       </c>
@@ -5616,7 +8626,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>780</v>
       </c>
@@ -5630,7 +8640,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>785</v>
       </c>
@@ -5644,7 +8654,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>790</v>
       </c>
@@ -5658,7 +8668,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>795</v>
       </c>
@@ -5672,7 +8682,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>800</v>
       </c>
@@ -5686,7 +8696,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>805</v>
       </c>
@@ -5700,7 +8710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>810</v>
       </c>
@@ -5714,7 +8724,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>815</v>
       </c>
@@ -5728,7 +8738,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>820</v>
       </c>
@@ -5742,7 +8752,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>825</v>
       </c>
@@ -5756,7 +8766,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>830</v>
       </c>
@@ -5770,7 +8780,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>835</v>
       </c>
@@ -5784,7 +8794,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>840</v>
       </c>
@@ -5798,7 +8808,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>845</v>
       </c>
@@ -5812,7 +8822,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>850</v>
       </c>
@@ -5826,7 +8836,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>855</v>
       </c>
@@ -5840,7 +8850,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>860</v>
       </c>
@@ -5854,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>865</v>
       </c>
@@ -5868,7 +8878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>870</v>
       </c>
@@ -5882,7 +8892,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>875</v>
       </c>
@@ -5896,7 +8906,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>880</v>
       </c>
@@ -5910,7 +8920,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>885</v>
       </c>
@@ -5924,7 +8934,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>890</v>
       </c>
@@ -5938,7 +8948,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>895</v>
       </c>
@@ -5952,7 +8962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>900</v>
       </c>
@@ -5966,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>905</v>
       </c>
@@ -5980,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B203">
         <v>910</v>
       </c>
@@ -5994,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B204">
         <v>915</v>
       </c>
@@ -6008,7 +9018,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B205">
         <v>920</v>
       </c>
@@ -6022,7 +9032,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B206">
         <v>925</v>
       </c>
@@ -6036,7 +9046,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B207">
         <v>930</v>
       </c>
@@ -6050,7 +9060,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B208">
         <v>935</v>
       </c>
@@ -6064,7 +9074,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B209">
         <v>940</v>
       </c>
@@ -6078,7 +9088,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B210">
         <v>945</v>
       </c>
@@ -6092,7 +9102,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B211">
         <v>950</v>
       </c>
@@ -6106,7 +9116,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B212">
         <v>955</v>
       </c>
@@ -6120,7 +9130,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B213">
         <v>960</v>
       </c>
@@ -6134,7 +9144,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B214">
         <v>965</v>
       </c>
@@ -6148,7 +9158,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B215">
         <v>970</v>
       </c>
@@ -6162,7 +9172,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B216">
         <v>975</v>
       </c>
@@ -6176,7 +9186,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B217">
         <v>980</v>
       </c>
@@ -6190,7 +9200,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B218">
         <v>985</v>
       </c>
@@ -6204,7 +9214,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B219">
         <v>990</v>
       </c>
@@ -6218,7 +9228,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B220">
         <v>995</v>
       </c>
@@ -6232,7 +9242,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B221">
         <v>1000</v>
       </c>

--- a/F_Knapsack/mochila.xlsx
+++ b/F_Knapsack/mochila.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\F_Knapsack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A615CAA5-BDFC-4A03-8D44-3C254FC1E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1F5509-7C82-4008-8DE8-A9E09E5B830B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,7 +1176,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>MEMOIZACION</c:v>
+            <c:v>Memoizacion Recursivo</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1345,7 +1345,7 @@
           <c:idx val="3"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Iterativo Memo</c:v>
+            <c:v>Memoizacio Iterativo</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
